--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1849,6 +1849,1026 @@
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>122405370</v>
+      </c>
+      <c r="B12" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>702790</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6633243</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>122405477</v>
+      </c>
+      <c r="B13" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>702729</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6633227</v>
+      </c>
+      <c r="S13" t="n">
+        <v>15</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>122405164</v>
+      </c>
+      <c r="B14" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>702809</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6633193</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>122405386</v>
+      </c>
+      <c r="B15" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>702761</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6633264</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>122405804</v>
+      </c>
+      <c r="B16" t="n">
+        <v>91472</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>3298</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Climacocystis borealis</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6633209</v>
+      </c>
+      <c r="S16" t="n">
+        <v>12</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>122405409</v>
+      </c>
+      <c r="B17" t="n">
+        <v>91339</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>3884</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dichomitus campestris</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Quél.) Domański &amp; Orlicz</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>702759</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6633237</v>
+      </c>
+      <c r="S17" t="n">
+        <v>12</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>122405689</v>
+      </c>
+      <c r="B18" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>702764</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6633291</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>122405320</v>
+      </c>
+      <c r="B19" t="n">
+        <v>100451</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6633209</v>
+      </c>
+      <c r="S19" t="n">
+        <v>12</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>122405288</v>
+      </c>
+      <c r="B20" t="n">
+        <v>92098</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>702791</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6633209</v>
+      </c>
+      <c r="S20" t="n">
+        <v>12</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>122405519</v>
+      </c>
+      <c r="B21" t="n">
+        <v>97139</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>221945</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Lycopodium annotinum</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Slänningen, Upl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>702729</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6633227</v>
+      </c>
+      <c r="S21" t="n">
+        <v>15</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Norrtälje</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Malsta</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-02-01</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Viktor Lund</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Viktor Lund, Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405370</v>
+        <v>122405320</v>
       </c>
       <c r="B12" t="n">
-        <v>92098</v>
+        <v>100451</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702790</v>
+        <v>702791</v>
       </c>
       <c r="R12" t="n">
-        <v>6633243</v>
+        <v>6633209</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405164</v>
+        <v>122405689</v>
       </c>
       <c r="B14" t="n">
-        <v>100451</v>
+        <v>92098</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702809</v>
+        <v>702764</v>
       </c>
       <c r="R14" t="n">
-        <v>6633193</v>
+        <v>6633291</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405386</v>
+        <v>122405370</v>
       </c>
       <c r="B15" t="n">
         <v>92098</v>
@@ -2197,10 +2197,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702761</v>
+        <v>702790</v>
       </c>
       <c r="R15" t="n">
-        <v>6633264</v>
+        <v>6633243</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405804</v>
+        <v>122405519</v>
       </c>
       <c r="B16" t="n">
-        <v>91472</v>
+        <v>97139</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3298</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R16" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2463,7 +2463,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405689</v>
+        <v>122405288</v>
       </c>
       <c r="B18" t="n">
         <v>92098</v>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702764</v>
+        <v>702791</v>
       </c>
       <c r="R18" t="n">
-        <v>6633291</v>
+        <v>6633209</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405320</v>
+        <v>122405386</v>
       </c>
       <c r="B19" t="n">
-        <v>100451</v>
+        <v>92098</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702791</v>
+        <v>702761</v>
       </c>
       <c r="R19" t="n">
-        <v>6633209</v>
+        <v>6633264</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405288</v>
+        <v>122405804</v>
       </c>
       <c r="B20" t="n">
-        <v>92098</v>
+        <v>91472</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405519</v>
+        <v>122405164</v>
       </c>
       <c r="B21" t="n">
-        <v>97139</v>
+        <v>100451</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R21" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405320</v>
+        <v>122405164</v>
       </c>
       <c r="B12" t="n">
-        <v>100451</v>
+        <v>100463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702791</v>
+        <v>702809</v>
       </c>
       <c r="R12" t="n">
-        <v>6633209</v>
+        <v>6633193</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405477</v>
+        <v>122405689</v>
       </c>
       <c r="B13" t="n">
-        <v>92098</v>
+        <v>92110</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702729</v>
+        <v>702764</v>
       </c>
       <c r="R13" t="n">
-        <v>6633227</v>
+        <v>6633291</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405689</v>
+        <v>122405370</v>
       </c>
       <c r="B14" t="n">
-        <v>92098</v>
+        <v>92110</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702764</v>
+        <v>702790</v>
       </c>
       <c r="R14" t="n">
-        <v>6633291</v>
+        <v>6633243</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405370</v>
+        <v>122405288</v>
       </c>
       <c r="B15" t="n">
-        <v>92098</v>
+        <v>92110</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702790</v>
+        <v>702791</v>
       </c>
       <c r="R15" t="n">
-        <v>6633243</v>
+        <v>6633209</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405519</v>
+        <v>122405320</v>
       </c>
       <c r="B16" t="n">
-        <v>97139</v>
+        <v>100463</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R16" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405409</v>
+        <v>122405519</v>
       </c>
       <c r="B17" t="n">
-        <v>91339</v>
+        <v>97151</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3884</v>
+        <v>221945</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702759</v>
+        <v>702729</v>
       </c>
       <c r="R17" t="n">
-        <v>6633237</v>
+        <v>6633227</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405288</v>
+        <v>122405804</v>
       </c>
       <c r="B18" t="n">
-        <v>92098</v>
+        <v>91484</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405386</v>
+        <v>122405477</v>
       </c>
       <c r="B19" t="n">
-        <v>92098</v>
+        <v>92110</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702761</v>
+        <v>702729</v>
       </c>
       <c r="R19" t="n">
-        <v>6633264</v>
+        <v>6633227</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405804</v>
+        <v>122405409</v>
       </c>
       <c r="B20" t="n">
-        <v>91472</v>
+        <v>91351</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>3884</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702791</v>
+        <v>702759</v>
       </c>
       <c r="R20" t="n">
-        <v>6633209</v>
+        <v>6633237</v>
       </c>
       <c r="S20" t="n">
         <v>12</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405164</v>
+        <v>122405386</v>
       </c>
       <c r="B21" t="n">
-        <v>100451</v>
+        <v>92110</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,10 +2809,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702809</v>
+        <v>702761</v>
       </c>
       <c r="R21" t="n">
-        <v>6633193</v>
+        <v>6633264</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405164</v>
+        <v>122405703</v>
       </c>
       <c r="B12" t="n">
-        <v>100463</v>
+        <v>92115</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702809</v>
+        <v>702764</v>
       </c>
       <c r="R12" t="n">
-        <v>6633193</v>
+        <v>6633291</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405689</v>
+        <v>122405320</v>
       </c>
       <c r="B13" t="n">
-        <v>92110</v>
+        <v>100468</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702764</v>
+        <v>702791</v>
       </c>
       <c r="R13" t="n">
-        <v>6633291</v>
+        <v>6633209</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405370</v>
+        <v>122405804</v>
       </c>
       <c r="B14" t="n">
-        <v>92110</v>
+        <v>91489</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702790</v>
+        <v>702791</v>
       </c>
       <c r="R14" t="n">
-        <v>6633243</v>
+        <v>6633209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405288</v>
+        <v>122405386</v>
       </c>
       <c r="B15" t="n">
-        <v>92110</v>
+        <v>92115</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702791</v>
+        <v>702761</v>
       </c>
       <c r="R15" t="n">
-        <v>6633209</v>
+        <v>6633264</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405320</v>
+        <v>122405164</v>
       </c>
       <c r="B16" t="n">
-        <v>100463</v>
+        <v>100468</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702791</v>
+        <v>702809</v>
       </c>
       <c r="R16" t="n">
-        <v>6633209</v>
+        <v>6633193</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405519</v>
+        <v>122405370</v>
       </c>
       <c r="B17" t="n">
-        <v>97151</v>
+        <v>92115</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702729</v>
+        <v>702790</v>
       </c>
       <c r="R17" t="n">
-        <v>6633227</v>
+        <v>6633243</v>
       </c>
       <c r="S17" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405804</v>
+        <v>122405409</v>
       </c>
       <c r="B18" t="n">
-        <v>91484</v>
+        <v>91356</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>3884</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702791</v>
+        <v>702759</v>
       </c>
       <c r="R18" t="n">
-        <v>6633209</v>
+        <v>6633237</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405477</v>
+        <v>122405519</v>
       </c>
       <c r="B19" t="n">
-        <v>92110</v>
+        <v>97156</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405409</v>
+        <v>122405477</v>
       </c>
       <c r="B20" t="n">
-        <v>91351</v>
+        <v>92115</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702759</v>
+        <v>702729</v>
       </c>
       <c r="R20" t="n">
-        <v>6633237</v>
+        <v>6633227</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405386</v>
+        <v>122405288</v>
       </c>
       <c r="B21" t="n">
-        <v>92110</v>
+        <v>92115</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R21" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405703</v>
+        <v>122405370</v>
       </c>
       <c r="B12" t="n">
-        <v>92115</v>
+        <v>92120</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1869,11 +1869,6 @@
       <c r="E12" t="n">
         <v>5964</v>
       </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
       <c r="G12" t="inlineStr">
         <is>
           <t>Sarcodon imbricatus</t>
@@ -1891,10 +1886,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702764</v>
+        <v>702790</v>
       </c>
       <c r="R12" t="n">
-        <v>6633291</v>
+        <v>6633243</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,10 +1948,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405320</v>
+        <v>122405804</v>
       </c>
       <c r="B13" t="n">
-        <v>100468</v>
+        <v>91494</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1964,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
+        <v>3298</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2055,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405804</v>
+        <v>122405386</v>
       </c>
       <c r="B14" t="n">
-        <v>91489</v>
+        <v>92120</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2061,16 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3298</v>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Trådticka</t>
-        </is>
+        <v>5964</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2080,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702791</v>
+        <v>702761</v>
       </c>
       <c r="R14" t="n">
-        <v>6633209</v>
+        <v>6633264</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,10 +2142,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405386</v>
+        <v>122405477</v>
       </c>
       <c r="B15" t="n">
-        <v>92115</v>
+        <v>92120</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2175,11 +2160,6 @@
       <c r="E15" t="n">
         <v>5964</v>
       </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Sarcodon imbricatus</t>
@@ -2197,13 +2177,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702761</v>
+        <v>702729</v>
       </c>
       <c r="R15" t="n">
-        <v>6633264</v>
+        <v>6633227</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2239,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405164</v>
+        <v>122405320</v>
       </c>
       <c r="B16" t="n">
-        <v>100468</v>
+        <v>100477</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2277,11 +2257,6 @@
       <c r="E16" t="n">
         <v>222498</v>
       </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Blåsippa</t>
-        </is>
-      </c>
       <c r="G16" t="inlineStr">
         <is>
           <t>Hepatica nobilis</t>
@@ -2299,13 +2274,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702809</v>
+        <v>702791</v>
       </c>
       <c r="R16" t="n">
-        <v>6633193</v>
+        <v>6633209</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,10 +2336,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405370</v>
+        <v>122405703</v>
       </c>
       <c r="B17" t="n">
-        <v>92115</v>
+        <v>92120</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2379,11 +2354,6 @@
       <c r="E17" t="n">
         <v>5964</v>
       </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
-      </c>
       <c r="G17" t="inlineStr">
         <is>
           <t>Sarcodon imbricatus</t>
@@ -2401,10 +2371,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702790</v>
+        <v>702764</v>
       </c>
       <c r="R17" t="n">
-        <v>6633243</v>
+        <v>6633291</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2463,10 +2433,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405409</v>
+        <v>122405288</v>
       </c>
       <c r="B18" t="n">
-        <v>91356</v>
+        <v>92120</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2449,16 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3884</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Hasselticka</t>
-        </is>
+        <v>5964</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2468,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702759</v>
+        <v>702791</v>
       </c>
       <c r="R18" t="n">
-        <v>6633237</v>
+        <v>6633209</v>
       </c>
       <c r="S18" t="n">
         <v>12</v>
@@ -2565,10 +2530,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405519</v>
+        <v>122405409</v>
       </c>
       <c r="B19" t="n">
-        <v>97156</v>
+        <v>91361</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2546,16 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>221945</v>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Revlummer</t>
-        </is>
+        <v>3884</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2565,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702729</v>
+        <v>702759</v>
       </c>
       <c r="R19" t="n">
-        <v>6633227</v>
+        <v>6633237</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2627,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405477</v>
+        <v>122405164</v>
       </c>
       <c r="B20" t="n">
-        <v>92115</v>
+        <v>100477</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2643,16 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
+        <v>222498</v>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2662,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R20" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2724,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405288</v>
+        <v>122405519</v>
       </c>
       <c r="B21" t="n">
-        <v>92115</v>
+        <v>97165</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2740,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Fjällig taggsvamp s.str.</t>
-        </is>
+        <v>221945</v>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2759,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R21" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405370</v>
+        <v>122405164</v>
       </c>
       <c r="B12" t="n">
-        <v>92120</v>
+        <v>100490</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,16 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>222498</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1886,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702790</v>
+        <v>702809</v>
       </c>
       <c r="R12" t="n">
-        <v>6633243</v>
+        <v>6633193</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1951,7 +1956,7 @@
         <v>122405804</v>
       </c>
       <c r="B13" t="n">
-        <v>91494</v>
+        <v>91507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1965,6 +1970,11 @@
       </c>
       <c r="E13" t="n">
         <v>3298</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trådticka</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -2045,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405386</v>
+        <v>122405703</v>
       </c>
       <c r="B14" t="n">
-        <v>92120</v>
+        <v>92133</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2063,6 +2073,11 @@
       <c r="E14" t="n">
         <v>5964</v>
       </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
       <c r="G14" t="inlineStr">
         <is>
           <t>Sarcodon imbricatus</t>
@@ -2080,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702761</v>
+        <v>702764</v>
       </c>
       <c r="R14" t="n">
-        <v>6633264</v>
+        <v>6633291</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2142,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405477</v>
+        <v>122405288</v>
       </c>
       <c r="B15" t="n">
-        <v>92120</v>
+        <v>92133</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,6 +2175,11 @@
       <c r="E15" t="n">
         <v>5964</v>
       </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
       <c r="G15" t="inlineStr">
         <is>
           <t>Sarcodon imbricatus</t>
@@ -2177,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R15" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2239,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405320</v>
+        <v>122405370</v>
       </c>
       <c r="B16" t="n">
-        <v>100477</v>
+        <v>92133</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2255,16 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>222498</v>
+        <v>5964</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2274,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702791</v>
+        <v>702790</v>
       </c>
       <c r="R16" t="n">
-        <v>6633209</v>
+        <v>6633243</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2336,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405703</v>
+        <v>122405409</v>
       </c>
       <c r="B17" t="n">
-        <v>92120</v>
+        <v>91374</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2352,16 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>3884</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Hasselticka</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2371,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702764</v>
+        <v>702759</v>
       </c>
       <c r="R17" t="n">
-        <v>6633291</v>
+        <v>6633237</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2433,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405288</v>
+        <v>122405519</v>
       </c>
       <c r="B18" t="n">
-        <v>92120</v>
+        <v>97178</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2449,16 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>221945</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Revlummer</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2468,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R18" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2530,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405409</v>
+        <v>122405477</v>
       </c>
       <c r="B19" t="n">
-        <v>91361</v>
+        <v>92133</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2546,16 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3884</v>
+        <v>5964</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2565,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702759</v>
+        <v>702729</v>
       </c>
       <c r="R19" t="n">
-        <v>6633237</v>
+        <v>6633227</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2627,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405164</v>
+        <v>122405386</v>
       </c>
       <c r="B20" t="n">
-        <v>100477</v>
+        <v>92133</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2643,16 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5964</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2662,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702809</v>
+        <v>702761</v>
       </c>
       <c r="R20" t="n">
-        <v>6633193</v>
+        <v>6633264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2724,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405519</v>
+        <v>122405320</v>
       </c>
       <c r="B21" t="n">
-        <v>97165</v>
+        <v>100490</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2740,16 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>222498</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2759,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R21" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405164</v>
+        <v>122405386</v>
       </c>
       <c r="B12" t="n">
-        <v>100490</v>
+        <v>92146</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702809</v>
+        <v>702761</v>
       </c>
       <c r="R12" t="n">
-        <v>6633193</v>
+        <v>6633264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405804</v>
+        <v>122405689</v>
       </c>
       <c r="B13" t="n">
-        <v>91507</v>
+        <v>92146</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702791</v>
+        <v>702764</v>
       </c>
       <c r="R13" t="n">
-        <v>6633209</v>
+        <v>6633291</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405703</v>
+        <v>122405409</v>
       </c>
       <c r="B14" t="n">
-        <v>92133</v>
+        <v>91387</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702764</v>
+        <v>702759</v>
       </c>
       <c r="R14" t="n">
-        <v>6633291</v>
+        <v>6633237</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405288</v>
+        <v>122405804</v>
       </c>
       <c r="B15" t="n">
-        <v>92133</v>
+        <v>91520</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2262,7 +2262,7 @@
         <v>122405370</v>
       </c>
       <c r="B16" t="n">
-        <v>92133</v>
+        <v>92146</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405409</v>
+        <v>122405288</v>
       </c>
       <c r="B17" t="n">
-        <v>91374</v>
+        <v>92146</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702759</v>
+        <v>702791</v>
       </c>
       <c r="R17" t="n">
-        <v>6633237</v>
+        <v>6633209</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405519</v>
+        <v>122405164</v>
       </c>
       <c r="B18" t="n">
-        <v>97178</v>
+        <v>100503</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R18" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405477</v>
+        <v>122405320</v>
       </c>
       <c r="B19" t="n">
-        <v>92133</v>
+        <v>100503</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R19" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405386</v>
+        <v>122405477</v>
       </c>
       <c r="B20" t="n">
-        <v>92133</v>
+        <v>92146</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702761</v>
+        <v>702729</v>
       </c>
       <c r="R20" t="n">
-        <v>6633264</v>
+        <v>6633227</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405320</v>
+        <v>122405519</v>
       </c>
       <c r="B21" t="n">
-        <v>100490</v>
+        <v>97191</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R21" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405689</v>
+        <v>122405409</v>
       </c>
       <c r="B13" t="n">
-        <v>92146</v>
+        <v>91387</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702764</v>
+        <v>702759</v>
       </c>
       <c r="R13" t="n">
-        <v>6633291</v>
+        <v>6633237</v>
       </c>
       <c r="S13" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405409</v>
+        <v>122405689</v>
       </c>
       <c r="B14" t="n">
-        <v>91387</v>
+        <v>92146</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702759</v>
+        <v>702764</v>
       </c>
       <c r="R14" t="n">
-        <v>6633237</v>
+        <v>6633291</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405386</v>
+        <v>122405320</v>
       </c>
       <c r="B12" t="n">
-        <v>92146</v>
+        <v>100503</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R12" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405409</v>
+        <v>122405519</v>
       </c>
       <c r="B13" t="n">
-        <v>91387</v>
+        <v>97191</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>3884</v>
+        <v>221945</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702759</v>
+        <v>702729</v>
       </c>
       <c r="R13" t="n">
-        <v>6633237</v>
+        <v>6633227</v>
       </c>
       <c r="S13" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405689</v>
+        <v>122405703</v>
       </c>
       <c r="B14" t="n">
         <v>92146</v>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405804</v>
+        <v>122405164</v>
       </c>
       <c r="B15" t="n">
-        <v>91520</v>
+        <v>100503</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702791</v>
+        <v>702809</v>
       </c>
       <c r="R15" t="n">
-        <v>6633209</v>
+        <v>6633193</v>
       </c>
       <c r="S15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,7 +2259,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405370</v>
+        <v>122405477</v>
       </c>
       <c r="B16" t="n">
         <v>92146</v>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702790</v>
+        <v>702729</v>
       </c>
       <c r="R16" t="n">
-        <v>6633243</v>
+        <v>6633227</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405164</v>
+        <v>122405386</v>
       </c>
       <c r="B18" t="n">
-        <v>100503</v>
+        <v>92146</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,10 +2503,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702809</v>
+        <v>702761</v>
       </c>
       <c r="R18" t="n">
-        <v>6633193</v>
+        <v>6633264</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405320</v>
+        <v>122405409</v>
       </c>
       <c r="B19" t="n">
-        <v>100503</v>
+        <v>91387</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>222498</v>
+        <v>3884</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,10 +2605,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702791</v>
+        <v>702759</v>
       </c>
       <c r="R19" t="n">
-        <v>6633209</v>
+        <v>6633237</v>
       </c>
       <c r="S19" t="n">
         <v>12</v>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405477</v>
+        <v>122405804</v>
       </c>
       <c r="B20" t="n">
-        <v>92146</v>
+        <v>91520</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R20" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S20" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405519</v>
+        <v>122405370</v>
       </c>
       <c r="B21" t="n">
-        <v>97191</v>
+        <v>92146</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702729</v>
+        <v>702790</v>
       </c>
       <c r="R21" t="n">
-        <v>6633227</v>
+        <v>6633243</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405320</v>
+        <v>122405689</v>
       </c>
       <c r="B12" t="n">
-        <v>100503</v>
+        <v>92147</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702791</v>
+        <v>702764</v>
       </c>
       <c r="R12" t="n">
-        <v>6633209</v>
+        <v>6633291</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>122405519</v>
       </c>
       <c r="B13" t="n">
-        <v>97191</v>
+        <v>97194</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405703</v>
+        <v>122405386</v>
       </c>
       <c r="B14" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2095,10 +2095,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702764</v>
+        <v>702761</v>
       </c>
       <c r="R14" t="n">
-        <v>6633291</v>
+        <v>6633264</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2160,7 +2160,7 @@
         <v>122405164</v>
       </c>
       <c r="B15" t="n">
-        <v>100503</v>
+        <v>100506</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405477</v>
+        <v>122405288</v>
       </c>
       <c r="B16" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R16" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S16" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405288</v>
+        <v>122405409</v>
       </c>
       <c r="B17" t="n">
-        <v>92146</v>
+        <v>91388</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,10 +2401,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702791</v>
+        <v>702759</v>
       </c>
       <c r="R17" t="n">
-        <v>6633209</v>
+        <v>6633237</v>
       </c>
       <c r="S17" t="n">
         <v>12</v>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405386</v>
+        <v>122405804</v>
       </c>
       <c r="B18" t="n">
-        <v>92146</v>
+        <v>91521</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R18" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405409</v>
+        <v>122405370</v>
       </c>
       <c r="B19" t="n">
-        <v>91387</v>
+        <v>92147</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702759</v>
+        <v>702790</v>
       </c>
       <c r="R19" t="n">
-        <v>6633237</v>
+        <v>6633243</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405804</v>
+        <v>122405320</v>
       </c>
       <c r="B20" t="n">
-        <v>91520</v>
+        <v>100506</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>222498</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405370</v>
+        <v>122405477</v>
       </c>
       <c r="B21" t="n">
-        <v>92146</v>
+        <v>92147</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702790</v>
+        <v>702729</v>
       </c>
       <c r="R21" t="n">
-        <v>6633243</v>
+        <v>6633227</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,7 +1851,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405689</v>
+        <v>122405386</v>
       </c>
       <c r="B12" t="n">
         <v>92147</v>
@@ -1891,10 +1891,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702764</v>
+        <v>702761</v>
       </c>
       <c r="R12" t="n">
-        <v>6633291</v>
+        <v>6633264</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405519</v>
+        <v>122405477</v>
       </c>
       <c r="B13" t="n">
-        <v>97194</v>
+        <v>92147</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>221945</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2055,7 +2055,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405386</v>
+        <v>122405288</v>
       </c>
       <c r="B14" t="n">
         <v>92147</v>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R14" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405164</v>
+        <v>122405519</v>
       </c>
       <c r="B15" t="n">
-        <v>100506</v>
+        <v>97194</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>222498</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702809</v>
+        <v>702729</v>
       </c>
       <c r="R15" t="n">
-        <v>6633193</v>
+        <v>6633227</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405288</v>
+        <v>122405409</v>
       </c>
       <c r="B16" t="n">
-        <v>92147</v>
+        <v>91388</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702791</v>
+        <v>702759</v>
       </c>
       <c r="R16" t="n">
-        <v>6633209</v>
+        <v>6633237</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405409</v>
+        <v>122405164</v>
       </c>
       <c r="B17" t="n">
-        <v>91388</v>
+        <v>100506</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>3884</v>
+        <v>222498</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702759</v>
+        <v>702809</v>
       </c>
       <c r="R17" t="n">
-        <v>6633237</v>
+        <v>6633193</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405804</v>
+        <v>122405689</v>
       </c>
       <c r="B18" t="n">
-        <v>91521</v>
+        <v>92147</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702791</v>
+        <v>702764</v>
       </c>
       <c r="R18" t="n">
-        <v>6633209</v>
+        <v>6633291</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405370</v>
+        <v>122405804</v>
       </c>
       <c r="B19" t="n">
-        <v>92147</v>
+        <v>91521</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702790</v>
+        <v>702791</v>
       </c>
       <c r="R19" t="n">
-        <v>6633243</v>
+        <v>6633209</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405320</v>
+        <v>122405370</v>
       </c>
       <c r="B20" t="n">
-        <v>100506</v>
+        <v>92147</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702791</v>
+        <v>702790</v>
       </c>
       <c r="R20" t="n">
-        <v>6633209</v>
+        <v>6633243</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405477</v>
+        <v>122405320</v>
       </c>
       <c r="B21" t="n">
-        <v>92147</v>
+        <v>100506</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R21" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405386</v>
+        <v>122405804</v>
       </c>
       <c r="B12" t="n">
-        <v>92147</v>
+        <v>91522</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R12" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405477</v>
+        <v>122405164</v>
       </c>
       <c r="B13" t="n">
-        <v>92147</v>
+        <v>100507</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,13 +1993,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R13" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S13" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405288</v>
+        <v>122405320</v>
       </c>
       <c r="B14" t="n">
-        <v>92147</v>
+        <v>100507</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>5964</v>
+        <v>222498</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
         <v>122405519</v>
       </c>
       <c r="B15" t="n">
-        <v>97194</v>
+        <v>97195</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405409</v>
+        <v>122405703</v>
       </c>
       <c r="B16" t="n">
-        <v>91388</v>
+        <v>92148</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702759</v>
+        <v>702764</v>
       </c>
       <c r="R16" t="n">
-        <v>6633237</v>
+        <v>6633291</v>
       </c>
       <c r="S16" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2361,10 +2361,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405164</v>
+        <v>122405288</v>
       </c>
       <c r="B17" t="n">
-        <v>100506</v>
+        <v>92148</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2377,21 +2377,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702809</v>
+        <v>702791</v>
       </c>
       <c r="R17" t="n">
-        <v>6633193</v>
+        <v>6633209</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405689</v>
+        <v>122405409</v>
       </c>
       <c r="B18" t="n">
-        <v>92147</v>
+        <v>91389</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702764</v>
+        <v>702759</v>
       </c>
       <c r="R18" t="n">
-        <v>6633291</v>
+        <v>6633237</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405804</v>
+        <v>122405477</v>
       </c>
       <c r="B19" t="n">
-        <v>91521</v>
+        <v>92148</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R19" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S19" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405370</v>
+        <v>122405386</v>
       </c>
       <c r="B20" t="n">
-        <v>92147</v>
+        <v>92148</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2707,10 +2707,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702790</v>
+        <v>702761</v>
       </c>
       <c r="R20" t="n">
-        <v>6633243</v>
+        <v>6633264</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405320</v>
+        <v>122405370</v>
       </c>
       <c r="B21" t="n">
-        <v>100506</v>
+        <v>92148</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702791</v>
+        <v>702790</v>
       </c>
       <c r="R21" t="n">
-        <v>6633209</v>
+        <v>6633243</v>
       </c>
       <c r="S21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405804</v>
+        <v>122405370</v>
       </c>
       <c r="B12" t="n">
-        <v>91522</v>
+        <v>92151</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702791</v>
+        <v>702790</v>
       </c>
       <c r="R12" t="n">
-        <v>6633209</v>
+        <v>6633243</v>
       </c>
       <c r="S12" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,10 +1953,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405164</v>
+        <v>122405703</v>
       </c>
       <c r="B13" t="n">
-        <v>100507</v>
+        <v>92151</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1969,21 +1969,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702809</v>
+        <v>702764</v>
       </c>
       <c r="R13" t="n">
-        <v>6633193</v>
+        <v>6633291</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2058,7 +2058,7 @@
         <v>122405320</v>
       </c>
       <c r="B14" t="n">
-        <v>100507</v>
+        <v>100510</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2157,10 +2157,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405519</v>
+        <v>122405164</v>
       </c>
       <c r="B15" t="n">
-        <v>97195</v>
+        <v>100510</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2173,21 +2173,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R15" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S15" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405703</v>
+        <v>122405409</v>
       </c>
       <c r="B16" t="n">
-        <v>92148</v>
+        <v>91392</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,13 +2299,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702764</v>
+        <v>702759</v>
       </c>
       <c r="R16" t="n">
-        <v>6633291</v>
+        <v>6633237</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2364,7 +2364,7 @@
         <v>122405288</v>
       </c>
       <c r="B17" t="n">
-        <v>92148</v>
+        <v>92151</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405409</v>
+        <v>122405477</v>
       </c>
       <c r="B18" t="n">
-        <v>91389</v>
+        <v>92151</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702759</v>
+        <v>702729</v>
       </c>
       <c r="R18" t="n">
-        <v>6633237</v>
+        <v>6633227</v>
       </c>
       <c r="S18" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405477</v>
+        <v>122405386</v>
       </c>
       <c r="B19" t="n">
-        <v>92148</v>
+        <v>92151</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702729</v>
+        <v>702761</v>
       </c>
       <c r="R19" t="n">
-        <v>6633227</v>
+        <v>6633264</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405386</v>
+        <v>122405804</v>
       </c>
       <c r="B20" t="n">
-        <v>92148</v>
+        <v>91525</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702761</v>
+        <v>702791</v>
       </c>
       <c r="R20" t="n">
-        <v>6633264</v>
+        <v>6633209</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405370</v>
+        <v>122405519</v>
       </c>
       <c r="B21" t="n">
-        <v>92148</v>
+        <v>97198</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702790</v>
+        <v>702729</v>
       </c>
       <c r="R21" t="n">
-        <v>6633243</v>
+        <v>6633227</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -1851,10 +1851,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>122405370</v>
+        <v>122405409</v>
       </c>
       <c r="B12" t="n">
-        <v>92151</v>
+        <v>91392</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1867,21 +1867,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>5964</v>
+        <v>3884</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Hasselticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Dichomitus campestris</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Quél.) Domański &amp; Orlicz</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1891,13 +1891,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>702790</v>
+        <v>702759</v>
       </c>
       <c r="R12" t="n">
-        <v>6633243</v>
+        <v>6633237</v>
       </c>
       <c r="S12" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1953,7 +1953,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>122405703</v>
+        <v>122405386</v>
       </c>
       <c r="B13" t="n">
         <v>92151</v>
@@ -1993,10 +1993,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>702764</v>
+        <v>702761</v>
       </c>
       <c r="R13" t="n">
-        <v>6633291</v>
+        <v>6633264</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2055,10 +2055,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>122405320</v>
+        <v>122405689</v>
       </c>
       <c r="B14" t="n">
-        <v>100510</v>
+        <v>92151</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2071,21 +2071,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>222498</v>
+        <v>5964</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2095,13 +2095,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>702791</v>
+        <v>702764</v>
       </c>
       <c r="R14" t="n">
-        <v>6633209</v>
+        <v>6633291</v>
       </c>
       <c r="S14" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2157,7 +2157,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>122405164</v>
+        <v>122405320</v>
       </c>
       <c r="B15" t="n">
         <v>100510</v>
@@ -2197,13 +2197,13 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>702809</v>
+        <v>702791</v>
       </c>
       <c r="R15" t="n">
-        <v>6633193</v>
+        <v>6633209</v>
       </c>
       <c r="S15" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T15" t="inlineStr">
         <is>
@@ -2259,10 +2259,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>122405409</v>
+        <v>122405288</v>
       </c>
       <c r="B16" t="n">
-        <v>91392</v>
+        <v>92151</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2275,21 +2275,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>3884</v>
+        <v>5964</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Hasselticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dichomitus campestris</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Quél.) Domański &amp; Orlicz</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2299,10 +2299,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>702759</v>
+        <v>702791</v>
       </c>
       <c r="R16" t="n">
-        <v>6633237</v>
+        <v>6633209</v>
       </c>
       <c r="S16" t="n">
         <v>12</v>
@@ -2361,7 +2361,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>122405288</v>
+        <v>122405477</v>
       </c>
       <c r="B17" t="n">
         <v>92151</v>
@@ -2401,13 +2401,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>702791</v>
+        <v>702729</v>
       </c>
       <c r="R17" t="n">
-        <v>6633209</v>
+        <v>6633227</v>
       </c>
       <c r="S17" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2463,10 +2463,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>122405477</v>
+        <v>122405804</v>
       </c>
       <c r="B18" t="n">
-        <v>92151</v>
+        <v>91525</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2479,21 +2479,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2503,13 +2503,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>702729</v>
+        <v>702791</v>
       </c>
       <c r="R18" t="n">
-        <v>6633227</v>
+        <v>6633209</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2565,10 +2565,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>122405386</v>
+        <v>122405519</v>
       </c>
       <c r="B19" t="n">
-        <v>92151</v>
+        <v>97198</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2581,21 +2581,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5964</v>
+        <v>221945</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2605,13 +2605,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>702761</v>
+        <v>702729</v>
       </c>
       <c r="R19" t="n">
-        <v>6633264</v>
+        <v>6633227</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405804</v>
+        <v>122405370</v>
       </c>
       <c r="B20" t="n">
-        <v>91525</v>
+        <v>92151</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2707,13 +2707,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>702791</v>
+        <v>702790</v>
       </c>
       <c r="R20" t="n">
-        <v>6633209</v>
+        <v>6633243</v>
       </c>
       <c r="S20" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405519</v>
+        <v>122405164</v>
       </c>
       <c r="B21" t="n">
-        <v>97198</v>
+        <v>100510</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221945</v>
+        <v>222498</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2809,13 +2809,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>702729</v>
+        <v>702809</v>
       </c>
       <c r="R21" t="n">
-        <v>6633227</v>
+        <v>6633193</v>
       </c>
       <c r="S21" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>

--- a/artfynd/A 60084-2024 artfynd.xlsx
+++ b/artfynd/A 60084-2024 artfynd.xlsx
@@ -2667,10 +2667,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>122405288</v>
+        <v>122405804</v>
       </c>
       <c r="B20" t="n">
-        <v>92254</v>
+        <v>91628</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2683,21 +2683,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>5964</v>
+        <v>3298</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2769,10 +2769,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>122405804</v>
+        <v>122405288</v>
       </c>
       <c r="B21" t="n">
-        <v>91628</v>
+        <v>92254</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2785,21 +2785,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>3298</v>
+        <v>5964</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
